--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554494448</v>
+        <v>46157.93110436123</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110436123</v>
+        <v>46157.93134577804</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93134577804</v>
+        <v>46157.93382246737</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93382246737</v>
+        <v>46157.93693929854</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93693929854</v>
+        <v>46158.28204167815</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204167815</v>
+        <v>46158.29651073436</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651073436</v>
+        <v>46158.29805832494</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29805832494</v>
+        <v>46158.33368927112</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33368927112</v>
+        <v>46158.37220736236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/2. ИП Мамедов Фариз (мойка)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220736236</v>
+        <v>46158.37274727179</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
